--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/16.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/16.xlsx
@@ -426,13 +426,13 @@
         <v>-12.63451968332076</v>
       </c>
       <c r="E2">
-        <v>-19.43937792096014</v>
+        <v>-19.65725639089118</v>
       </c>
       <c r="F2">
-        <v>-2.355115771166129</v>
+        <v>-2.499344476402356</v>
       </c>
       <c r="G2">
-        <v>-13.71616125620772</v>
+        <v>-12.94474606758226</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.86274145365875</v>
       </c>
       <c r="E3">
-        <v>-19.97864671968955</v>
+        <v>-20.52961709525479</v>
       </c>
       <c r="F3">
-        <v>-2.505232511901455</v>
+        <v>-2.690681607468389</v>
       </c>
       <c r="G3">
-        <v>-13.70533322506155</v>
+        <v>-11.99534757790785</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.05855085504642</v>
       </c>
       <c r="E4">
-        <v>-20.34455194798333</v>
+        <v>-20.59890727604616</v>
       </c>
       <c r="F4">
-        <v>-2.466440066428354</v>
+        <v>-2.595437580229308</v>
       </c>
       <c r="G4">
-        <v>-13.15864233859935</v>
+        <v>-12.70138770818293</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.1906254215376</v>
       </c>
       <c r="E5">
-        <v>-20.86356488247644</v>
+        <v>-20.67652079206362</v>
       </c>
       <c r="F5">
-        <v>-2.51020188795085</v>
+        <v>-2.208870819671487</v>
       </c>
       <c r="G5">
-        <v>-13.27599194645133</v>
+        <v>-12.45428547498427</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.27108557165044</v>
       </c>
       <c r="E6">
-        <v>-21.39624022305068</v>
+        <v>-21.83582372344925</v>
       </c>
       <c r="F6">
-        <v>-2.279966280384158</v>
+        <v>-2.277298108979741</v>
       </c>
       <c r="G6">
-        <v>-13.05296075461275</v>
+        <v>-12.18811606330367</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.28927010832899</v>
       </c>
       <c r="E7">
-        <v>-21.73770527712506</v>
+        <v>-21.60699993184167</v>
       </c>
       <c r="F7">
-        <v>-2.440887417154198</v>
+        <v>-2.826841185833947</v>
       </c>
       <c r="G7">
-        <v>-13.1689617804038</v>
+        <v>-11.05279043518488</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.25212685343602</v>
       </c>
       <c r="E8">
-        <v>-22.25175500410576</v>
+        <v>-22.69389256384466</v>
       </c>
       <c r="F8">
-        <v>-2.052836222210561</v>
+        <v>-2.275668710298434</v>
       </c>
       <c r="G8">
-        <v>-12.83944510529656</v>
+        <v>-11.30461106498602</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.16873344576981</v>
       </c>
       <c r="E9">
-        <v>-22.40158862359755</v>
+        <v>-22.14181724062155</v>
       </c>
       <c r="F9">
-        <v>-2.0890358777129</v>
+        <v>-2.247809057807481</v>
       </c>
       <c r="G9">
-        <v>-12.73254618811142</v>
+        <v>-11.09186978395787</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.04098614740222</v>
       </c>
       <c r="E10">
-        <v>-23.94932141299111</v>
+        <v>-23.80369927432645</v>
       </c>
       <c r="F10">
-        <v>-1.774127039334251</v>
+        <v>-2.223865926396964</v>
       </c>
       <c r="G10">
-        <v>-12.29798776722168</v>
+        <v>-11.4611450207009</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.8815978302288</v>
       </c>
       <c r="E11">
-        <v>-24.11664852757453</v>
+        <v>-23.66774542766817</v>
       </c>
       <c r="F11">
-        <v>-1.952424010745414</v>
+        <v>-1.854829076817187</v>
       </c>
       <c r="G11">
-        <v>-11.97679226998919</v>
+        <v>-11.04106006810987</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.70715595696372</v>
       </c>
       <c r="E12">
-        <v>-24.40587763397043</v>
+        <v>-23.58093458094113</v>
       </c>
       <c r="F12">
-        <v>-1.898783079577132</v>
+        <v>-1.983810851637487</v>
       </c>
       <c r="G12">
-        <v>-11.73311891332015</v>
+        <v>-10.9310636777726</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.5212046845959</v>
       </c>
       <c r="E13">
-        <v>-24.50011517807005</v>
+        <v>-24.66327609656641</v>
       </c>
       <c r="F13">
-        <v>-1.985653969108716</v>
+        <v>-1.330635699223452</v>
       </c>
       <c r="G13">
-        <v>-10.92511810430689</v>
+        <v>-10.38224984096144</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.33754143859298</v>
       </c>
       <c r="E14">
-        <v>-25.77931398728276</v>
+        <v>-24.30749200767978</v>
       </c>
       <c r="F14">
-        <v>-1.740293201134308</v>
+        <v>-1.55132768594249</v>
       </c>
       <c r="G14">
-        <v>-10.51452900690889</v>
+        <v>-9.485137616836777</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.16406480886829</v>
       </c>
       <c r="E15">
-        <v>-26.53244902797243</v>
+        <v>-25.37293778678244</v>
       </c>
       <c r="F15">
-        <v>-1.359034618893627</v>
+        <v>-1.25793320574935</v>
       </c>
       <c r="G15">
-        <v>-9.927462689157721</v>
+        <v>-9.395632455138244</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.99194439990258</v>
       </c>
       <c r="E16">
-        <v>-27.08652140823292</v>
+        <v>-27.40122770939597</v>
       </c>
       <c r="F16">
-        <v>-1.451338770220173</v>
+        <v>-1.395871288928718</v>
       </c>
       <c r="G16">
-        <v>-9.669374926178039</v>
+        <v>-9.65180726594877</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.8198194733651</v>
       </c>
       <c r="E17">
-        <v>-28.14606658570358</v>
+        <v>-26.88368652895536</v>
       </c>
       <c r="F17">
-        <v>-1.30133551581903</v>
+        <v>-1.006939539435906</v>
       </c>
       <c r="G17">
-        <v>-9.320485918983842</v>
+        <v>-9.021274606199636</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.63785306920697</v>
       </c>
       <c r="E18">
-        <v>-28.44831505487153</v>
+        <v>-27.65690535186904</v>
       </c>
       <c r="F18">
-        <v>-1.096611967523758</v>
+        <v>-0.9761068763363052</v>
       </c>
       <c r="G18">
-        <v>-8.931132887518572</v>
+        <v>-8.837769009266133</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.42485226051247</v>
       </c>
       <c r="E19">
-        <v>-29.14648347805609</v>
+        <v>-27.89408870649478</v>
       </c>
       <c r="F19">
-        <v>-1.142081882630825</v>
+        <v>-0.9200446272496402</v>
       </c>
       <c r="G19">
-        <v>-8.589994125647783</v>
+        <v>-8.963676042945144</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.17275846359852</v>
       </c>
       <c r="E20">
-        <v>-29.45247699522839</v>
+        <v>-28.47877809952113</v>
       </c>
       <c r="F20">
-        <v>-0.8593079009089777</v>
+        <v>-0.2816856542020769</v>
       </c>
       <c r="G20">
-        <v>-8.524792972040057</v>
+        <v>-8.361883602835187</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.86872184892938</v>
       </c>
       <c r="E21">
-        <v>-30.62760467903383</v>
+        <v>-31.11112343425481</v>
       </c>
       <c r="F21">
-        <v>-0.5614998791937218</v>
+        <v>-0.3347077949204676</v>
       </c>
       <c r="G21">
-        <v>-8.073490477532472</v>
+        <v>-8.027970090838295</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.4965743221612</v>
       </c>
       <c r="E22">
-        <v>-31.62955898831194</v>
+        <v>-29.98383681410341</v>
       </c>
       <c r="F22">
-        <v>-0.563217913187128</v>
+        <v>-0.08299013549697622</v>
       </c>
       <c r="G22">
-        <v>-8.17035213796728</v>
+        <v>-7.485049327947894</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.05793049319362</v>
       </c>
       <c r="E23">
-        <v>-31.36788564625272</v>
+        <v>-30.30040884655762</v>
       </c>
       <c r="F23">
-        <v>-0.5649914477965218</v>
+        <v>0.4544596056437598</v>
       </c>
       <c r="G23">
-        <v>-7.992388524247676</v>
+        <v>-8.202583577345704</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.552900468603257</v>
       </c>
       <c r="E24">
-        <v>-32.00744429459301</v>
+        <v>-31.67001863933347</v>
       </c>
       <c r="F24">
-        <v>-0.3702331593569272</v>
+        <v>0.2750153453797197</v>
       </c>
       <c r="G24">
-        <v>-7.264751393668335</v>
+        <v>-7.086948559805145</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.984731566039088</v>
       </c>
       <c r="E25">
-        <v>-32.20017161988545</v>
+        <v>-32.34172492465422</v>
       </c>
       <c r="F25">
-        <v>-0.2691582539695399</v>
+        <v>0.0159956273005507</v>
       </c>
       <c r="G25">
-        <v>-7.630184319965252</v>
+        <v>-8.193222252236609</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.376689659855959</v>
       </c>
       <c r="E26">
-        <v>-32.41670739727322</v>
+        <v>-31.13769878396883</v>
       </c>
       <c r="F26">
-        <v>-0.07387726569877887</v>
+        <v>0.04610429729010433</v>
       </c>
       <c r="G26">
-        <v>-7.130191778737067</v>
+        <v>-7.085603258965772</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.750040254292176</v>
       </c>
       <c r="E27">
-        <v>-32.8349255573036</v>
+        <v>-32.26111808731768</v>
       </c>
       <c r="F27">
-        <v>-0.2947846279425454</v>
+        <v>0.6344779245179399</v>
       </c>
       <c r="G27">
-        <v>-7.440532995050908</v>
+        <v>-7.727725193262866</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.12526147947714</v>
       </c>
       <c r="E28">
-        <v>-32.74507157604341</v>
+        <v>-32.27115092148168</v>
       </c>
       <c r="F28">
-        <v>-0.2909575705416117</v>
+        <v>0.8203428605210791</v>
       </c>
       <c r="G28">
-        <v>-7.539648854697054</v>
+        <v>-8.071003311590411</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.53198279692498</v>
       </c>
       <c r="E29">
-        <v>-32.93572486024033</v>
+        <v>-32.41967581198525</v>
       </c>
       <c r="F29">
-        <v>-0.1746837800476591</v>
+        <v>0.1459449352473204</v>
       </c>
       <c r="G29">
-        <v>-7.729313304497636</v>
+        <v>-7.349082068967624</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.987858824584756</v>
       </c>
       <c r="E30">
-        <v>-33.06820536733473</v>
+        <v>-31.78748725509244</v>
       </c>
       <c r="F30">
-        <v>-0.3146828413251924</v>
+        <v>0.3823262005753817</v>
       </c>
       <c r="G30">
-        <v>-7.773029019334118</v>
+        <v>-7.31140052057896</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.503072235787777</v>
       </c>
       <c r="E31">
-        <v>-32.79080689928387</v>
+        <v>-32.31171246316838</v>
       </c>
       <c r="F31">
-        <v>-0.2222975099931719</v>
+        <v>0.5633832921726724</v>
       </c>
       <c r="G31">
-        <v>-8.221818098127169</v>
+        <v>-8.070931124716104</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.090645769637419</v>
       </c>
       <c r="E32">
-        <v>-32.11561595321423</v>
+        <v>-32.02282978503407</v>
       </c>
       <c r="F32">
-        <v>-0.2574741317530529</v>
+        <v>0.5624720880295929</v>
       </c>
       <c r="G32">
-        <v>-7.841983890405849</v>
+        <v>-8.159688167899084</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.749258009340929</v>
       </c>
       <c r="E33">
-        <v>-32.24468425514385</v>
+        <v>-32.68336432497789</v>
       </c>
       <c r="F33">
-        <v>-0.1890667232624669</v>
+        <v>0.2970747693162705</v>
       </c>
       <c r="G33">
-        <v>-8.048297258399055</v>
+        <v>-7.979122545482841</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.470794998616562</v>
       </c>
       <c r="E34">
-        <v>-32.01360075500644</v>
+        <v>-30.82358797713778</v>
       </c>
       <c r="F34">
-        <v>-0.1454680901183233</v>
+        <v>0.7178473050378906</v>
       </c>
       <c r="G34">
-        <v>-7.900274791409385</v>
+        <v>-7.768819212073351</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.25017342574845</v>
       </c>
       <c r="E35">
-        <v>-31.59650339229295</v>
+        <v>-31.85589211921531</v>
       </c>
       <c r="F35">
-        <v>-0.2559789285909998</v>
+        <v>-0.1867464661672255</v>
       </c>
       <c r="G35">
-        <v>-8.267492702234641</v>
+        <v>-7.916326527278188</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.073364302454443</v>
       </c>
       <c r="E36">
-        <v>-31.63372065592499</v>
+        <v>-30.60284071892288</v>
       </c>
       <c r="F36">
-        <v>-0.1257529459316951</v>
+        <v>0.3643174932385204</v>
       </c>
       <c r="G36">
-        <v>-8.605140244366179</v>
+        <v>-8.093249993763447</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.926242458053109</v>
       </c>
       <c r="E37">
-        <v>-31.1565145934707</v>
+        <v>-30.7311437087452</v>
       </c>
       <c r="F37">
-        <v>-0.0008268579155016587</v>
+        <v>0.2932021517081829</v>
       </c>
       <c r="G37">
-        <v>-8.096406528903634</v>
+        <v>-8.111401711430295</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.801876494408776</v>
       </c>
       <c r="E38">
-        <v>-30.8423720873216</v>
+        <v>-30.72768169036634</v>
       </c>
       <c r="F38">
-        <v>-0.01377921062567473</v>
+        <v>0.2884556064901417</v>
       </c>
       <c r="G38">
-        <v>-8.414048463187239</v>
+        <v>-8.426484292897534</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.690924758671079</v>
       </c>
       <c r="E39">
-        <v>-30.05287566458735</v>
+        <v>-29.99496780321426</v>
       </c>
       <c r="F39">
-        <v>-0.130570730746377</v>
+        <v>-0.01297072404054241</v>
       </c>
       <c r="G39">
-        <v>-8.667637671408924</v>
+        <v>-7.90379226092111</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.586579239280775</v>
       </c>
       <c r="E40">
-        <v>-29.75255632534666</v>
+        <v>-29.98159748370662</v>
       </c>
       <c r="F40">
-        <v>-0.2357899582499702</v>
+        <v>0.2781109543639815</v>
       </c>
       <c r="G40">
-        <v>-8.907324343883241</v>
+        <v>-8.437568259325339</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.488398977869054</v>
       </c>
       <c r="E41">
-        <v>-28.93927862136113</v>
+        <v>-28.58910531177</v>
       </c>
       <c r="F41">
-        <v>0.07247371682342099</v>
+        <v>0.4981071124646685</v>
       </c>
       <c r="G41">
-        <v>-8.506286882444789</v>
+        <v>-9.207720177650405</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.395587638574312</v>
       </c>
       <c r="E42">
-        <v>-29.1463113960438</v>
+        <v>-28.97345501469702</v>
       </c>
       <c r="F42">
-        <v>0.1089989207150596</v>
+        <v>0.4613988393770113</v>
       </c>
       <c r="G42">
-        <v>-8.417017968698536</v>
+        <v>-7.987886688268119</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.309398750964647</v>
       </c>
       <c r="E43">
-        <v>-28.35774557471812</v>
+        <v>-28.0318946990222</v>
       </c>
       <c r="F43">
-        <v>-0.1132321726383806</v>
+        <v>0.3528040147070101</v>
       </c>
       <c r="G43">
-        <v>-8.503592999544484</v>
+        <v>-8.553057414553114</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.236201526636238</v>
       </c>
       <c r="E44">
-        <v>-27.72794352362736</v>
+        <v>-28.33274386972178</v>
       </c>
       <c r="F44">
-        <v>0.01187118600201196</v>
+        <v>0.7054806080814968</v>
       </c>
       <c r="G44">
-        <v>-8.545855133230132</v>
+        <v>-8.354353199356261</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.183051329019645</v>
       </c>
       <c r="E45">
-        <v>-27.10037853869639</v>
+        <v>-27.62737970133903</v>
       </c>
       <c r="F45">
-        <v>0.05313382307026094</v>
+        <v>0.303625498737609</v>
       </c>
       <c r="G45">
-        <v>-8.855845258837112</v>
+        <v>-8.12218708669619</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.1565158666107</v>
       </c>
       <c r="E46">
-        <v>-26.53086406206974</v>
+        <v>-26.77081884278818</v>
       </c>
       <c r="F46">
-        <v>0.1408049155129494</v>
+        <v>0.08573670730964388</v>
       </c>
       <c r="G46">
-        <v>-8.252592675133201</v>
+        <v>-8.140365054135515</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.165215009744188</v>
       </c>
       <c r="E47">
-        <v>-26.38917263884374</v>
+        <v>-27.00800672588793</v>
       </c>
       <c r="F47">
-        <v>0.1002538460437052</v>
+        <v>0.2101989095802696</v>
       </c>
       <c r="G47">
-        <v>-9.230462324278916</v>
+        <v>-7.950139515448266</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.216843021686576</v>
       </c>
       <c r="E48">
-        <v>-25.64263105630924</v>
+        <v>-25.91402250358893</v>
       </c>
       <c r="F48">
-        <v>0.1564850820805413</v>
+        <v>0.3852561360790835</v>
       </c>
       <c r="G48">
-        <v>-9.083194538247918</v>
+        <v>-7.835785662880058</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.314584194856255</v>
       </c>
       <c r="E49">
-        <v>-24.87322973698403</v>
+        <v>-25.75855999090561</v>
       </c>
       <c r="F49">
-        <v>0.1977352936377482</v>
+        <v>0.1250742185337868</v>
       </c>
       <c r="G49">
-        <v>-8.894366799944994</v>
+        <v>-7.447774651032602</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.460988262591324</v>
       </c>
       <c r="E50">
-        <v>-24.5234685185276</v>
+        <v>-23.75184824693863</v>
       </c>
       <c r="F50">
-        <v>0.230045764183943</v>
+        <v>0.4214922397471451</v>
       </c>
       <c r="G50">
-        <v>-8.564859968502436</v>
+        <v>-7.79003887189828</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.656279965609732</v>
       </c>
       <c r="E51">
-        <v>-24.59125524594842</v>
+        <v>-23.79008215298539</v>
       </c>
       <c r="F51">
-        <v>0.2001458427798948</v>
+        <v>0.4246102146512825</v>
       </c>
       <c r="G51">
-        <v>-9.290899144182328</v>
+        <v>-8.436117959396064</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.894299503045975</v>
       </c>
       <c r="E52">
-        <v>-23.6179910837459</v>
+        <v>-24.79914843069255</v>
       </c>
       <c r="F52">
-        <v>0.2552803203754243</v>
+        <v>0.1599600833352852</v>
       </c>
       <c r="G52">
-        <v>-8.985086013620521</v>
+        <v>-8.066691786461302</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.168534608551418</v>
       </c>
       <c r="E53">
-        <v>-23.34867367756173</v>
+        <v>-23.84321021004338</v>
       </c>
       <c r="F53">
-        <v>0.4314972612381575</v>
+        <v>0.1190801520071296</v>
       </c>
       <c r="G53">
-        <v>-8.803066810053444</v>
+        <v>-7.979388324429157</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.471334523589322</v>
       </c>
       <c r="E54">
-        <v>-22.39148106961243</v>
+        <v>-21.94708380134371</v>
       </c>
       <c r="F54">
-        <v>0.2301973554186553</v>
+        <v>0.4066114477232547</v>
       </c>
       <c r="G54">
-        <v>-9.267100444211675</v>
+        <v>-8.309282340015727</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.789880133918675</v>
       </c>
       <c r="E55">
-        <v>-22.35411210210113</v>
+        <v>-23.47243234371735</v>
       </c>
       <c r="F55">
-        <v>0.16459231385174</v>
+        <v>0.3166018741024633</v>
       </c>
       <c r="G55">
-        <v>-9.70192136282617</v>
+        <v>-8.259381522539693</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.114114714476832</v>
       </c>
       <c r="E56">
-        <v>-21.75917024392142</v>
+        <v>-21.20932745838409</v>
       </c>
       <c r="F56">
-        <v>0.139459646850803</v>
+        <v>0.5043364353337209</v>
       </c>
       <c r="G56">
-        <v>-9.619424890378612</v>
+        <v>-7.857182508669197</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.435899612430921</v>
       </c>
       <c r="E57">
-        <v>-21.50600590452261</v>
+        <v>-21.99323800842988</v>
       </c>
       <c r="F57">
-        <v>0.2879138542087108</v>
+        <v>0.2455768246190309</v>
       </c>
       <c r="G57">
-        <v>-9.39347013013057</v>
+        <v>-8.544230928558207</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.743955273152004</v>
       </c>
       <c r="E58">
-        <v>-20.10910752737653</v>
+        <v>-21.112449813938</v>
       </c>
       <c r="F58">
-        <v>0.1444041718781133</v>
+        <v>0.7967642107677939</v>
       </c>
       <c r="G58">
-        <v>-9.611431834659804</v>
+        <v>-9.038464925949567</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.032208153982396</v>
       </c>
       <c r="E59">
-        <v>-20.29741506203749</v>
+        <v>-20.13267370611245</v>
       </c>
       <c r="F59">
-        <v>0.1210798309174876</v>
+        <v>0.3849910585101877</v>
       </c>
       <c r="G59">
-        <v>-9.707223816866232</v>
+        <v>-8.945068235481534</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.297467650780325</v>
       </c>
       <c r="E60">
-        <v>-20.14534437638591</v>
+        <v>-21.06040406216784</v>
       </c>
       <c r="F60">
-        <v>-0.006960918533231998</v>
+        <v>0.3752527713228767</v>
       </c>
       <c r="G60">
-        <v>-10.13661431379985</v>
+        <v>-8.492364659368064</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.534301198244653</v>
       </c>
       <c r="E61">
-        <v>-19.71588201539448</v>
+        <v>-21.15141280429999</v>
       </c>
       <c r="F61">
-        <v>-0.1165199628600918</v>
+        <v>0.200756349555758</v>
       </c>
       <c r="G61">
-        <v>-10.1043599058705</v>
+        <v>-8.778529835231916</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.743287968891782</v>
       </c>
       <c r="E62">
-        <v>-19.49345242908573</v>
+        <v>-20.81951641580383</v>
       </c>
       <c r="F62">
-        <v>-0.2951184600058736</v>
+        <v>0.3629871351896244</v>
       </c>
       <c r="G62">
-        <v>-10.21201678523589</v>
+        <v>-8.778585615998427</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.926599620617798</v>
       </c>
       <c r="E63">
-        <v>-19.9719989198463</v>
+        <v>-20.18787580426595</v>
       </c>
       <c r="F63">
-        <v>-0.144068977574995</v>
+        <v>0.09423078665795001</v>
       </c>
       <c r="G63">
-        <v>-10.51367260808188</v>
+        <v>-9.210384529556674</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.083329963501737</v>
       </c>
       <c r="E64">
-        <v>-18.97414061530812</v>
+        <v>-19.75958631804251</v>
       </c>
       <c r="F64">
-        <v>-0.2173007978194853</v>
+        <v>0.4687000696652861</v>
       </c>
       <c r="G64">
-        <v>-10.59938467765769</v>
+        <v>-8.77939935894517</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.217381342392267</v>
       </c>
       <c r="E65">
-        <v>-19.05784040039189</v>
+        <v>-19.3104160381697</v>
       </c>
       <c r="F65">
-        <v>-0.106797414653434</v>
+        <v>0.2392290452113783</v>
       </c>
       <c r="G65">
-        <v>-10.55951127326732</v>
+        <v>-9.930097510069956</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.331445578288332</v>
       </c>
       <c r="E66">
-        <v>-19.08040578637211</v>
+        <v>-20.26108311507395</v>
       </c>
       <c r="F66">
-        <v>-0.3333865489130024</v>
+        <v>0.02080844191081583</v>
       </c>
       <c r="G66">
-        <v>-10.7878416379244</v>
+        <v>-10.08708427436003</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.424580761331272</v>
       </c>
       <c r="E67">
-        <v>-18.52460352904069</v>
+        <v>-19.96475788990803</v>
       </c>
       <c r="F67">
-        <v>-0.5592922800652611</v>
+        <v>-0.6563868800821968</v>
       </c>
       <c r="G67">
-        <v>-10.54469983914799</v>
+        <v>-10.85922789417168</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.500257373900828</v>
       </c>
       <c r="E68">
-        <v>-18.32815379811394</v>
+        <v>-18.89544026552881</v>
       </c>
       <c r="F68">
-        <v>-0.5783886338019981</v>
+        <v>-0.3053802753917539</v>
       </c>
       <c r="G68">
-        <v>-10.82788894705742</v>
+        <v>-9.666635106175901</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.5591399819829</v>
       </c>
       <c r="E69">
-        <v>-17.93742800378412</v>
+        <v>-19.5616829469593</v>
       </c>
       <c r="F69">
-        <v>-0.5645143081725092</v>
+        <v>-0.3533692557707349</v>
       </c>
       <c r="G69">
-        <v>-10.79333440281491</v>
+        <v>-8.847386269656864</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.599320532642746</v>
       </c>
       <c r="E70">
-        <v>-17.39002606573693</v>
+        <v>-19.27058358079823</v>
       </c>
       <c r="F70">
-        <v>-0.6592952780334259</v>
+        <v>-0.5930101468288123</v>
       </c>
       <c r="G70">
-        <v>-10.55143618700953</v>
+        <v>-10.00136892356266</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.623062841947763</v>
       </c>
       <c r="E71">
-        <v>-18.73726519691489</v>
+        <v>-19.41287276259324</v>
       </c>
       <c r="F71">
-        <v>-0.887265300753461</v>
+        <v>-0.4183546785203561</v>
       </c>
       <c r="G71">
-        <v>-10.65583153214482</v>
+        <v>-10.27276860240901</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.628841269799683</v>
       </c>
       <c r="E72">
-        <v>-17.8979759382293</v>
+        <v>-17.6089777840078</v>
       </c>
       <c r="F72">
-        <v>-0.9757026330437391</v>
+        <v>-0.3182688438119114</v>
       </c>
       <c r="G72">
-        <v>-10.1737380545234</v>
+        <v>-10.41575767552649</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.614604316003375</v>
       </c>
       <c r="E73">
-        <v>-17.92387428107917</v>
+        <v>-18.00219876751584</v>
       </c>
       <c r="F73">
-        <v>-0.9655849535859459</v>
+        <v>-0.5307359705885538</v>
       </c>
       <c r="G73">
-        <v>-10.02430466226317</v>
+        <v>-10.26624225272727</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.583428908132131</v>
       </c>
       <c r="E74">
-        <v>-18.38085617861521</v>
+        <v>-19.95814178938282</v>
       </c>
       <c r="F74">
-        <v>-1.183583917878483</v>
+        <v>-0.645618932213206</v>
       </c>
       <c r="G74">
-        <v>-10.28757019286366</v>
+        <v>-9.812793839319808</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.535087802026524</v>
       </c>
       <c r="E75">
-        <v>-18.84823545247286</v>
+        <v>-19.05069446840778</v>
       </c>
       <c r="F75">
-        <v>-1.370054390453069</v>
+        <v>-0.3879370274895582</v>
       </c>
       <c r="G75">
-        <v>-10.35070089566738</v>
+        <v>-9.700943558801455</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.470750829773309</v>
       </c>
       <c r="E76">
-        <v>-18.75239030010052</v>
+        <v>-19.80949463008104</v>
       </c>
       <c r="F76">
-        <v>-1.252686326620018</v>
+        <v>-1.010735118875533</v>
       </c>
       <c r="G76">
-        <v>-9.775742285470558</v>
+        <v>-9.315360650907989</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.39645731170334</v>
       </c>
       <c r="E77">
-        <v>-18.71798295459023</v>
+        <v>-21.64920530959316</v>
       </c>
       <c r="F77">
-        <v>-1.320939658773683</v>
+        <v>-0.6950708094255309</v>
       </c>
       <c r="G77">
-        <v>-9.464334672149898</v>
+        <v>-9.62102940772118</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.31324291514204</v>
       </c>
       <c r="E78">
-        <v>-19.40628836138609</v>
+        <v>-20.05885505131341</v>
       </c>
       <c r="F78">
-        <v>-1.409137592884552</v>
+        <v>-1.406534862504956</v>
       </c>
       <c r="G78">
-        <v>-9.432109795214592</v>
+        <v>-9.838997674693532</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.223045309615716</v>
       </c>
       <c r="E79">
-        <v>-19.33229309610076</v>
+        <v>-20.74625929178174</v>
       </c>
       <c r="F79">
-        <v>-1.375444577143085</v>
+        <v>-0.9620809594721039</v>
       </c>
       <c r="G79">
-        <v>-9.422430191614229</v>
+        <v>-9.070338712178014</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.130140302422639</v>
       </c>
       <c r="E80">
-        <v>-20.43801965150164</v>
+        <v>-20.9946098633104</v>
       </c>
       <c r="F80">
-        <v>-1.579505431516118</v>
+        <v>-1.481270169585528</v>
       </c>
       <c r="G80">
-        <v>-8.672881063460915</v>
+        <v>-8.696656794880653</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.031746669537131</v>
       </c>
       <c r="E81">
-        <v>-20.34989554731238</v>
+        <v>-20.83925150552925</v>
       </c>
       <c r="F81">
-        <v>-1.512103661052531</v>
+        <v>-1.193506102629216</v>
       </c>
       <c r="G81">
-        <v>-8.738879553907587</v>
+        <v>-7.998422690695495</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.926200432279314</v>
       </c>
       <c r="E82">
-        <v>-20.93229806096485</v>
+        <v>-22.46259169695488</v>
       </c>
       <c r="F82">
-        <v>-1.514462023048301</v>
+        <v>-1.147786020566503</v>
       </c>
       <c r="G82">
-        <v>-8.22926647106711</v>
+        <v>-7.765833300454257</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.813862493107516</v>
       </c>
       <c r="E83">
-        <v>-22.17643289593618</v>
+        <v>-22.30258259636785</v>
       </c>
       <c r="F83">
-        <v>-1.518131690642703</v>
+        <v>-1.400140694522747</v>
       </c>
       <c r="G83">
-        <v>-8.04419245022819</v>
+        <v>-8.797492014623948</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.689088029940753</v>
       </c>
       <c r="E84">
-        <v>-22.54657677590113</v>
+        <v>-23.7713161566976</v>
       </c>
       <c r="F84">
-        <v>-1.71026902461984</v>
+        <v>-0.9367221481702027</v>
       </c>
       <c r="G84">
-        <v>-8.397478294312043</v>
+        <v>-8.783740415068316</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.549722221484243</v>
       </c>
       <c r="E85">
-        <v>-24.038994255291</v>
+        <v>-24.42181333400342</v>
       </c>
       <c r="F85">
-        <v>-1.719825070978535</v>
+        <v>-1.475290185304718</v>
       </c>
       <c r="G85">
-        <v>-7.698689663683339</v>
+        <v>-7.250704484172352</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.39734053473188</v>
       </c>
       <c r="E86">
-        <v>-24.73183266456853</v>
+        <v>-25.90948950110725</v>
       </c>
       <c r="F86">
-        <v>-1.668284879543753</v>
+        <v>-1.416983888923869</v>
       </c>
       <c r="G86">
-        <v>-7.841652487028345</v>
+        <v>-7.324538531702977</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.229849601098366</v>
       </c>
       <c r="E87">
-        <v>-25.56935581839113</v>
+        <v>-26.55926665104585</v>
       </c>
       <c r="F87">
-        <v>-1.860625163534575</v>
+        <v>-1.33594056407098</v>
       </c>
       <c r="G87">
-        <v>-7.051199650914994</v>
+        <v>-7.288632124177973</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.05092683823391</v>
       </c>
       <c r="E88">
-        <v>-27.34743849513286</v>
+        <v>-27.15878679644732</v>
       </c>
       <c r="F88">
-        <v>-2.090543506385995</v>
+        <v>-1.87160434509128</v>
       </c>
       <c r="G88">
-        <v>-7.256820681159157</v>
+        <v>-7.9998139286367</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.86979380544729</v>
       </c>
       <c r="E89">
-        <v>-28.24085660363214</v>
+        <v>-29.55383103623106</v>
       </c>
       <c r="F89">
-        <v>-2.029265856131304</v>
+        <v>-1.592829721190148</v>
       </c>
       <c r="G89">
-        <v>-7.479159535248691</v>
+        <v>-6.55616175424157</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.692307458085689</v>
       </c>
       <c r="E90">
-        <v>-30.13172998248291</v>
+        <v>-30.42019604100852</v>
       </c>
       <c r="F90">
-        <v>-1.8272552110802</v>
+        <v>-1.684300534909478</v>
       </c>
       <c r="G90">
-        <v>-6.859835528346619</v>
+        <v>-7.368930178180705</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.528258462435583</v>
       </c>
       <c r="E91">
-        <v>-31.32830451918868</v>
+        <v>-32.5988924350758</v>
       </c>
       <c r="F91">
-        <v>-2.110424324053183</v>
+        <v>-1.807581485263712</v>
       </c>
       <c r="G91">
-        <v>-6.850972948914559</v>
+        <v>-5.983555779902873</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.392072977179486</v>
       </c>
       <c r="E92">
-        <v>-32.27156980532738</v>
+        <v>-33.71466767429971</v>
       </c>
       <c r="F92">
-        <v>-2.262944986991434</v>
+        <v>-1.765442435483301</v>
       </c>
       <c r="G92">
-        <v>-6.969897543115073</v>
+        <v>-6.524806401019516</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.292130262086942</v>
       </c>
       <c r="E93">
-        <v>-34.14917249109868</v>
+        <v>-34.81178786484902</v>
       </c>
       <c r="F93">
-        <v>-2.34014054525832</v>
+        <v>-2.675611947676661</v>
       </c>
       <c r="G93">
-        <v>-6.948074138523206</v>
+        <v>-6.627236294440702</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.237294563658748</v>
       </c>
       <c r="E94">
-        <v>-35.80367764064509</v>
+        <v>-37.22045601868484</v>
       </c>
       <c r="F94">
-        <v>-2.543986852474028</v>
+        <v>-1.948488437214713</v>
       </c>
       <c r="G94">
-        <v>-6.884976247935085</v>
+        <v>-7.134539397303331</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.23797478581386</v>
       </c>
       <c r="E95">
-        <v>-37.19708456433125</v>
+        <v>-37.97905919173876</v>
       </c>
       <c r="F95">
-        <v>-2.598946544547566</v>
+        <v>-1.931845707725068</v>
       </c>
       <c r="G95">
-        <v>-7.910026581884054</v>
+        <v>-7.940223663895624</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.298112909017211</v>
       </c>
       <c r="E96">
-        <v>-39.58943436208043</v>
+        <v>-40.48716357783501</v>
       </c>
       <c r="F96">
-        <v>-2.723567793359529</v>
+        <v>-2.487805318481359</v>
       </c>
       <c r="G96">
-        <v>-7.47467082415537</v>
+        <v>-7.445428577617599</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.412703824553325</v>
       </c>
       <c r="E97">
-        <v>-41.34845669172388</v>
+        <v>-43.25319399374913</v>
       </c>
       <c r="F97">
-        <v>-2.730912927120153</v>
+        <v>-2.716699799222919</v>
       </c>
       <c r="G97">
-        <v>-8.250072696975549</v>
+        <v>-7.493370505822646</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.588764527771136</v>
       </c>
       <c r="E98">
-        <v>-42.81495771436784</v>
+        <v>-44.51308565403014</v>
       </c>
       <c r="F98">
-        <v>-2.83748570695992</v>
+        <v>-2.502116193732124</v>
       </c>
       <c r="G98">
-        <v>-7.904714284179313</v>
+        <v>-7.786058750146673</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.804295669433527</v>
       </c>
       <c r="E99">
-        <v>-45.09113177568724</v>
+        <v>-46.54506401872292</v>
       </c>
       <c r="F99">
-        <v>-2.926574964396202</v>
+        <v>-3.355447276582395</v>
       </c>
       <c r="G99">
-        <v>-8.344650627204983</v>
+        <v>-8.024984179219199</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.067117531053283</v>
       </c>
       <c r="E100">
-        <v>-47.65489563581176</v>
+        <v>-47.34395023231207</v>
       </c>
       <c r="F100">
-        <v>-3.052924187610405</v>
+        <v>-3.651384016334727</v>
       </c>
       <c r="G100">
-        <v>-8.646490198458302</v>
+        <v>-8.50964685332166</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.340337941387413</v>
       </c>
       <c r="E101">
-        <v>-49.16239180152866</v>
+        <v>-49.59178283905447</v>
       </c>
       <c r="F101">
-        <v>-3.223716978719607</v>
+        <v>-3.167986904961464</v>
       </c>
       <c r="G101">
-        <v>-9.114940356835545</v>
+        <v>-8.01381490103085</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.659975562693422</v>
       </c>
       <c r="E102">
-        <v>-51.62451859102503</v>
+        <v>-51.17166552966548</v>
       </c>
       <c r="F102">
-        <v>-3.569417061827716</v>
+        <v>-3.537735322140246</v>
       </c>
       <c r="G102">
-        <v>-9.097494101803978</v>
+        <v>-8.796576553808864</v>
       </c>
     </row>
   </sheetData>
